--- a/app/tests/Fixtures/Cobranca/importacao/toplife_amostra_zip64.xlsx
+++ b/app/tests/Fixtures/Cobranca/importacao/toplife_amostra_zip64.xlsx
@@ -215,7 +215,7 @@
     <t>Total de inadimplência</t>
   </si>
   <si>
-    <t>Filtros:  Inadimplência até:08/07/2026; Competência: Todas</t>
+    <t>Filtros:  Inadimplência até:08/07/2026; Competência: Todas; Período de vencimento: Todos; Unidade: Todas; Sacado: Todos</t>
   </si>
   <si>
     <t>CONDOMINIO EXEMPLO - Rua Ficticia, 0, Cidade/UF</t>
